--- a/public/templates/en/control-checklist.xlsx
+++ b/public/templates/en/control-checklist.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J58"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -521,7 +521,7 @@
         <v>Assign every AI use case a named business owner who is accountable for its outcomes, and record the technical, data and risk contacts alongside them.</v>
       </c>
       <c r="E4" t="str">
-        <v>UAE AI Charter: Governance and accountability; Dubai AI Ethics: Accountability; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.3.2; NIST AI RMF: GOVERN 2.1</v>
+        <v>UAE AI Charter: Governance and accountability; UAE Gov Services Code: Agentic Reference p.9; Dubai AI Ethics: Accountability; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.3.2; NIST AI RMF: GOVERN 2.1</v>
       </c>
       <c r="F4" t="str">
         <v>Needs verification</v>
@@ -617,7 +617,7 @@
         <v>Require a documented go/no-go decision by an authorised committee or executive before a high-risk system goes live, based on test results and the residual risk.</v>
       </c>
       <c r="E7" t="str">
-        <v>SDAIA AI Ethics: Accountability &amp; Responsibility, Reliability &amp; Safety; ISO/IEC 42001: A.6.2.5; NIST AI RMF: MANAGE 1.1, GOVERN 2.3</v>
+        <v>UAE Gov Services Code: Code 2.1, Code 8.8, Agentic Guide §06; SDAIA AI Ethics: Accountability &amp; Responsibility, Reliability &amp; Safety; ISO/IEC 42001: A.6.2.5; NIST AI RMF: MANAGE 1.1, GOVERN 2.3</v>
       </c>
       <c r="F7" t="str">
         <v>Verified</v>
@@ -681,7 +681,7 @@
         <v>Train staff who build, operate or rely on AI systems in what the systems can and cannot do and in their own responsibilities, proportionate to their role.</v>
       </c>
       <c r="E9" t="str">
-        <v>UAE AI Charter: Promoting AI awareness for an inclusive society; ISO/IEC 42001: A.4.6; NIST AI RMF: GOVERN 2.2, MAP 3.4; EU AI Act: Art. 4</v>
+        <v>UAE AI Charter: Promoting AI awareness for an inclusive society; UAE Gov Services Code: Code 6.2; ISO/IEC 42001: A.4.6; NIST AI RMF: GOVERN 2.2, MAP 3.4; EU AI Act: Art. 4</v>
       </c>
       <c r="F9" t="str">
         <v>Needs verification</v>
@@ -733,25 +733,25 @@
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>CTL-TRA-01</v>
+        <v>CTL-ACC-09</v>
       </c>
       <c r="B11" t="str">
-        <v>Transparency</v>
+        <v>Accountability</v>
       </c>
       <c r="C11" t="str">
-        <v>Disclose AI interaction</v>
+        <v>Governance review for each agent</v>
       </c>
       <c r="D11" t="str">
-        <v>Tell people clearly when they are dealing with an AI system rather than a person, at the start of the interaction.</v>
+        <v>Run a documented governance review of each AI agent before launch, and again whenever its scope, permissions, data or outputs change. Record each decision to continue, modify or stop in a review log kept for that agent.</v>
       </c>
       <c r="E11" t="str">
-        <v>UAE AI Charter: Transparency; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; EU AI Act: Art. 50</v>
+        <v>UAE Gov Services Code: Code 2.1, Agentic Guide §06; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.2.5; NIST AI RMF: MANAGE 1.1</v>
       </c>
       <c r="F11" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G11" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H11" t="str">
         <v/>
@@ -765,25 +765,25 @@
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>CTL-TRA-02</v>
+        <v>CTL-ACC-10</v>
       </c>
       <c r="B12" t="str">
-        <v>Transparency</v>
+        <v>Accountability</v>
       </c>
       <c r="C12" t="str">
-        <v>Label AI-generated content</v>
+        <v>Approved scope document for each agent</v>
       </c>
       <c r="D12" t="str">
-        <v>Mark text, images, audio or video produced by generative AI as AI-generated before it is published or sent to the public.</v>
+        <v>Keep an approved, current scope document for each agent that lists the services and cases it may handle, its permissions and access limits, and which decisions it may take alone or must refer to a person. Re-approve it after any material change and block use outside it.</v>
       </c>
       <c r="E12" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; EU AI Act: Art. 50</v>
+        <v>UAE Gov Services Code: Code 5.4, Agentic Guide §05; NIST AI RMF: MAP 3.3</v>
       </c>
       <c r="F12" t="str">
         <v>Verified</v>
       </c>
       <c r="G12" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H12" t="str">
         <v/>
@@ -797,25 +797,25 @@
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>CTL-TRA-03</v>
+        <v>CTL-ACC-11</v>
       </c>
       <c r="B13" t="str">
-        <v>Transparency</v>
+        <v>Accountability</v>
       </c>
       <c r="C13" t="str">
-        <v>Explanation on request</v>
+        <v>Classify systems against the national agentic definition</v>
       </c>
       <c r="D13" t="str">
-        <v>Provide a simple way for a person affected by a significant AI-informed decision to ask for, and receive, a plain-language explanation of the main factors behind it.</v>
+        <v>Before registering an AI system, classify it as generative, agentic or multi-agent using the national definition and self-assessment criteria. Do not label chatbots, scripted automation, reply-drafting copilots or avatar interfaces as agentic unless they meet every criterion.</v>
       </c>
       <c r="E13" t="str">
-        <v>Dubai AI Ethics: Explainability; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; NIST AI RMF: MEASURE 2.9; EU AI Act: Art. 86</v>
+        <v>UAE Gov Services Code: Agentic Reference p.6, Agentic Reference p.7, Agentic Reference p.9, Agentic Reference p.13, Agentic Reference p.14; NIST AI RMF: MAP 2.1</v>
       </c>
       <c r="F13" t="str">
         <v>Verified</v>
       </c>
       <c r="G13" t="str">
-        <v>High risk</v>
+        <v>Little or no risk</v>
       </c>
       <c r="H13" t="str">
         <v/>
@@ -829,25 +829,25 @@
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>CTL-TRA-04</v>
+        <v>CTL-TRA-01</v>
       </c>
       <c r="B14" t="str">
         <v>Transparency</v>
       </c>
       <c r="C14" t="str">
-        <v>Notify people of AI-informed decisions</v>
+        <v>Disclose AI interaction</v>
       </c>
       <c r="D14" t="str">
-        <v>Inform people when a decision that significantly affects them is made or supported by an AI system, including employees affected by AI used at work.</v>
+        <v>Tell people clearly when they are dealing with an AI system rather than a person, at the start of the interaction.</v>
       </c>
       <c r="E14" t="str">
-        <v>Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.5; EU AI Act: Art. 26</v>
+        <v>UAE AI Charter: Transparency; UAE Gov Services Code: Code 5.6, Agentic Guide §06; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; EU AI Act: Art. 50</v>
       </c>
       <c r="F14" t="str">
-        <v>Verified</v>
+        <v>Needs verification</v>
       </c>
       <c r="G14" t="str">
-        <v>High risk</v>
+        <v>Little or no risk</v>
       </c>
       <c r="H14" t="str">
         <v/>
@@ -861,25 +861,25 @@
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>CTL-TRA-05</v>
+        <v>CTL-TRA-02</v>
       </c>
       <c r="B15" t="str">
         <v>Transparency</v>
       </c>
       <c r="C15" t="str">
-        <v>System documentation</v>
+        <v>Label AI-generated content</v>
       </c>
       <c r="D15" t="str">
-        <v>Maintain documentation for each system covering its purpose, design, data, model version, test results and known limitations, detailed enough for a reviewer to understand it.</v>
+        <v>Mark text, images, audio or video produced by generative AI as AI-generated before it is published or sent to the public.</v>
       </c>
       <c r="E15" t="str">
-        <v>Dubai AI Ethics: Transparency; SDAIA AI Ethics: Reliability &amp; Safety, Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.3, A.6.2.7; NIST AI RMF: MAP 2.1, MAP 2.2; EU AI Act: Art. 11</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; EU AI Act: Art. 50</v>
       </c>
       <c r="F15" t="str">
         <v>Verified</v>
       </c>
       <c r="G15" t="str">
-        <v>Limited risk</v>
+        <v>Little or no risk</v>
       </c>
       <c r="H15" t="str">
         <v/>
@@ -893,25 +893,25 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>CTL-TRA-06</v>
+        <v>CTL-TRA-03</v>
       </c>
       <c r="B16" t="str">
         <v>Transparency</v>
       </c>
       <c r="C16" t="str">
-        <v>Public statement of AI use</v>
+        <v>Explanation on request</v>
       </c>
       <c r="D16" t="str">
-        <v>Publish a plain-language summary of where the organisation uses AI in services to the public, what data it relies on and how to raise a concern.</v>
+        <v>Provide a simple way for a person affected by a significant AI-informed decision to ask for, and receive, a plain-language explanation of the main factors behind it.</v>
       </c>
       <c r="E16" t="str">
-        <v>Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.5; NIST AI RMF: GOVERN 4.2</v>
+        <v>UAE Gov Services Code: Code 5.6; Dubai AI Ethics: Explainability; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; NIST AI RMF: MEASURE 2.9; EU AI Act: Art. 86</v>
       </c>
       <c r="F16" t="str">
         <v>Verified</v>
       </c>
       <c r="G16" t="str">
-        <v>Limited risk</v>
+        <v>High risk</v>
       </c>
       <c r="H16" t="str">
         <v/>
@@ -925,25 +925,25 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>CTL-TRA-07</v>
+        <v>CTL-TRA-04</v>
       </c>
       <c r="B17" t="str">
         <v>Transparency</v>
       </c>
       <c r="C17" t="str">
-        <v>Instructions for operators</v>
+        <v>Notify people of AI-informed decisions</v>
       </c>
       <c r="D17" t="str">
-        <v>Give the people who operate or rely on a system written instructions on its intended use, accuracy, limits and when not to trust its output.</v>
+        <v>Inform people when a decision that significantly affects them is made or supported by an AI system, including employees affected by AI used at work.</v>
       </c>
       <c r="E17" t="str">
-        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; NIST AI RMF: MAP 2.2; EU AI Act: Art. 13</v>
+        <v>UAE Gov Services Code: Code 5.6; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.5; EU AI Act: Art. 26</v>
       </c>
       <c r="F17" t="str">
         <v>Verified</v>
       </c>
       <c r="G17" t="str">
-        <v>Limited risk</v>
+        <v>High risk</v>
       </c>
       <c r="H17" t="str">
         <v/>
@@ -957,25 +957,25 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>CTL-DAT-01</v>
+        <v>CTL-TRA-05</v>
       </c>
       <c r="B18" t="str">
-        <v>Data</v>
+        <v>Transparency</v>
       </c>
       <c r="C18" t="str">
-        <v>Data sources and provenance</v>
+        <v>System documentation</v>
       </c>
       <c r="D18" t="str">
-        <v>Record where each dataset used to build, tune or run the system comes from, the right to use it, and how it was collected and prepared.</v>
+        <v>Maintain documentation for each system covering its purpose, design, data, model version, test results and known limitations, detailed enough for a reviewer to understand it.</v>
       </c>
       <c r="E18" t="str">
-        <v>Dubai AI Ethics: Privacy; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.7.2, A.7.3, A.7.5; NIST AI RMF: MAP 2.3; EU AI Act: Art. 10</v>
+        <v>Dubai AI Ethics: Transparency; SDAIA AI Ethics: Reliability &amp; Safety, Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.3, A.6.2.7; NIST AI RMF: MAP 2.1, MAP 2.2; EU AI Act: Art. 11</v>
       </c>
       <c r="F18" t="str">
         <v>Verified</v>
       </c>
       <c r="G18" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H18" t="str">
         <v/>
@@ -989,19 +989,19 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>CTL-DAT-02</v>
+        <v>CTL-TRA-06</v>
       </c>
       <c r="B19" t="str">
-        <v>Data</v>
+        <v>Transparency</v>
       </c>
       <c r="C19" t="str">
-        <v>Data quality and representativeness</v>
+        <v>Public statement of AI use</v>
       </c>
       <c r="D19" t="str">
-        <v>Check that training and input data are accurate, complete and representative of the people the system will affect, and document the checks and any gaps.</v>
+        <v>Publish a plain-language summary of where the organisation uses AI in services to the public, what data it relies on and how to raise a concern.</v>
       </c>
       <c r="E19" t="str">
-        <v>Dubai AI Ethics: Fairness; SDAIA AI Ethics: Fairness, Accountability &amp; Responsibility; ISO/IEC 42001: A.7.4, A.7.6; NIST AI RMF: MAP 2.3; EU AI Act: Art. 10</v>
+        <v>Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.5; NIST AI RMF: GOVERN 4.2</v>
       </c>
       <c r="F19" t="str">
         <v>Verified</v>
@@ -1021,25 +1021,25 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>CTL-DAT-03</v>
+        <v>CTL-TRA-07</v>
       </c>
       <c r="B20" t="str">
-        <v>Data</v>
+        <v>Transparency</v>
       </c>
       <c r="C20" t="str">
-        <v>Privacy review and data minimisation</v>
+        <v>Instructions for operators</v>
       </c>
       <c r="D20" t="str">
-        <v>Where personal data is involved, complete a privacy review and use only the minimum personal data the purpose needs, in line with the organisation's data protection policy.</v>
+        <v>Give the people who operate or rely on a system written instructions on its intended use, accuracy, limits and when not to trust its output.</v>
       </c>
       <c r="E20" t="str">
-        <v>UAE AI Charter: Data privacy; Dubai AI Ethics: Privacy; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.2.3, A.7.3; NIST AI RMF: MEASURE 2.10</v>
+        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; NIST AI RMF: MAP 2.2; EU AI Act: Art. 13</v>
       </c>
       <c r="F20" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G20" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H20" t="str">
         <v/>
@@ -1053,19 +1053,19 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>CTL-DAT-04</v>
+        <v>CTL-TRA-08</v>
       </c>
       <c r="B21" t="str">
-        <v>Data</v>
+        <v>Transparency</v>
       </c>
       <c r="C21" t="str">
-        <v>Sensitive attributes justified</v>
+        <v>Show the data sources an agent used</v>
       </c>
       <c r="D21" t="str">
-        <v>Do not use sensitive attributes (or close proxies for them) as model inputs unless there is a documented, approved justification such as bias testing.</v>
+        <v>When an agent delivers a service, tell the customer which data sources it relied on and, before it acts, which of their data it will use.</v>
       </c>
       <c r="E21" t="str">
-        <v>Dubai AI Ethics: Fairness; SDAIA AI Ethics: Fairness; ISO/IEC 42001: A.7.4; NIST AI RMF: MEASURE 2.11; EU AI Act: Art. 10</v>
+        <v>UAE Gov Services Code: Code 5.2, Agentic Guide §03; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2</v>
       </c>
       <c r="F21" t="str">
         <v>Verified</v>
@@ -1085,22 +1085,22 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>CTL-DAT-05</v>
+        <v>CTL-TRA-09</v>
       </c>
       <c r="B22" t="str">
-        <v>Data</v>
+        <v>Transparency</v>
       </c>
       <c r="C22" t="str">
-        <v>Bias and fairness testing</v>
+        <v>Clear notice when the AI cannot finish</v>
       </c>
       <c r="D22" t="str">
-        <v>Test outcomes across relevant groups before launch and after major changes, set an acceptable threshold in advance, and record the results and any mitigations.</v>
+        <v>If the AI cannot complete a service, tell the customer promptly and in plain language what went wrong and what the next steps are, including how to reach a person.</v>
       </c>
       <c r="E22" t="str">
-        <v>UAE AI Charter: Algorithmic bias; Dubai AI Ethics: Fairness; SDAIA AI Ethics: Fairness; ISO/IEC 42001: A.5.4, A.6.2.4; NIST AI RMF: MEASURE 2.11; EU AI Act: Art. 10</v>
+        <v>UAE Gov Services Code: Code 4.5, Agentic Guide §03</v>
       </c>
       <c r="F22" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G22" t="str">
         <v>Limited risk</v>
@@ -1117,19 +1117,19 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>CTL-DAT-06</v>
+        <v>CTL-DAT-01</v>
       </c>
       <c r="B23" t="str">
         <v>Data</v>
       </c>
       <c r="C23" t="str">
-        <v>Rules for data in generative AI tools</v>
+        <v>Data sources and provenance</v>
       </c>
       <c r="D23" t="str">
-        <v>Set clear rules on what information staff may enter into generative AI tools, and block personal, sensitive or classified data from external services unless explicitly approved.</v>
+        <v>Record where each dataset used to build, tune or run the system comes from, the right to use it, and how it was collected and prepared.</v>
       </c>
       <c r="E23" t="str">
-        <v>Dubai AI Ethics: Privacy; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.2.3, A.9.2; NIST AI RMF: GOVERN 6.1, MEASURE 2.10</v>
+        <v>Dubai AI Ethics: Privacy; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.7.2, A.7.3, A.7.5; NIST AI RMF: MAP 2.3; EU AI Act: Art. 10</v>
       </c>
       <c r="F23" t="str">
         <v>Verified</v>
@@ -1149,19 +1149,19 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>CTL-DAT-07</v>
+        <v>CTL-DAT-02</v>
       </c>
       <c r="B24" t="str">
         <v>Data</v>
       </c>
       <c r="C24" t="str">
-        <v>Rights to training and grounding content</v>
+        <v>Data quality and representativeness</v>
       </c>
       <c r="D24" t="str">
-        <v>Confirm the organisation has the right to use the documents and content used to train, fine-tune or ground a model, and keep a record of that check.</v>
+        <v>Check that training and input data are accurate, complete and representative of the people the system will affect, and document the checks and any gaps.</v>
       </c>
       <c r="E24" t="str">
-        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.7.3, A.7.5; NIST AI RMF: MAP 4.1, GOVERN 6.1; EU AI Act: Art. 53</v>
+        <v>UAE Gov Services Code: Code 5.3; Dubai AI Ethics: Fairness; SDAIA AI Ethics: Fairness, Accountability &amp; Responsibility; ISO/IEC 42001: A.7.4, A.7.6; NIST AI RMF: MAP 2.3; EU AI Act: Art. 10</v>
       </c>
       <c r="F24" t="str">
         <v>Verified</v>
@@ -1181,25 +1181,25 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>CTL-HUM-01</v>
+        <v>CTL-DAT-03</v>
       </c>
       <c r="B25" t="str">
-        <v>Human oversight</v>
+        <v>Data</v>
       </c>
       <c r="C25" t="str">
-        <v>Defined human oversight model</v>
+        <v>Privacy review and data minimisation</v>
       </c>
       <c r="D25" t="str">
-        <v>Decide and document, for each use case, where humans review, approve or monitor the system's outputs, and assign that role to people with the competence and authority to act.</v>
+        <v>Where personal data is involved, complete a privacy review and use only the minimum personal data the purpose needs, in line with the organisation's data protection policy.</v>
       </c>
       <c r="E25" t="str">
-        <v>UAE AI Charter: Human oversight; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.1.3; NIST AI RMF: MAP 3.5, GOVERN 3.2; EU AI Act: Art. 14, Art. 26</v>
+        <v>UAE AI Charter: Data privacy; UAE Gov Services Code: Code 5.2, Code 5.7, Data Sharing Policy Art. 5; Dubai AI Ethics: Privacy; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.2.3, A.7.3; NIST AI RMF: MEASURE 2.10</v>
       </c>
       <c r="F25" t="str">
         <v>Needs verification</v>
       </c>
       <c r="G25" t="str">
-        <v>Limited risk</v>
+        <v>Little or no risk</v>
       </c>
       <c r="H25" t="str">
         <v/>
@@ -1213,19 +1213,19 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>CTL-HUM-02</v>
+        <v>CTL-DAT-04</v>
       </c>
       <c r="B26" t="str">
-        <v>Human oversight</v>
+        <v>Data</v>
       </c>
       <c r="C26" t="str">
-        <v>Right to challenge a decision</v>
+        <v>Sensitive attributes justified</v>
       </c>
       <c r="D26" t="str">
-        <v>Give people a clear route to challenge a significant AI-informed decision and have it reviewed by a human who can change it.</v>
+        <v>Do not use sensitive attributes (or close proxies for them) as model inputs unless there is a documented, approved justification such as bias testing.</v>
       </c>
       <c r="E26" t="str">
-        <v>Dubai AI Ethics: Accountability; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.3; NIST AI RMF: MEASURE 3.3</v>
+        <v>Dubai AI Ethics: Fairness; SDAIA AI Ethics: Fairness; ISO/IEC 42001: A.7.4; NIST AI RMF: MEASURE 2.11; EU AI Act: Art. 10</v>
       </c>
       <c r="F26" t="str">
         <v>Verified</v>
@@ -1245,25 +1245,25 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>CTL-HUM-03</v>
+        <v>CTL-DAT-05</v>
       </c>
       <c r="B27" t="str">
-        <v>Human oversight</v>
+        <v>Data</v>
       </c>
       <c r="C27" t="str">
-        <v>Guard against over-reliance</v>
+        <v>Bias and fairness testing</v>
       </c>
       <c r="D27" t="str">
-        <v>Train reviewers to question AI outputs rather than rubber-stamp them, and check periodically how often they override the system.</v>
+        <v>Test outcomes across relevant groups before launch and after major changes, set an acceptable threshold in advance, and record the results and any mitigations.</v>
       </c>
       <c r="E27" t="str">
-        <v>ISO/IEC 42001: A.4.6; NIST AI RMF: MAP 3.4, GOVERN 3.2; EU AI Act: Art. 14</v>
+        <v>UAE AI Charter: Algorithmic bias; Dubai AI Ethics: Fairness; SDAIA AI Ethics: Fairness; ISO/IEC 42001: A.5.4, A.6.2.4; NIST AI RMF: MEASURE 2.11; EU AI Act: Art. 10</v>
       </c>
       <c r="F27" t="str">
-        <v>Verified</v>
+        <v>Needs verification</v>
       </c>
       <c r="G27" t="str">
-        <v>High risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H27" t="str">
         <v/>
@@ -1277,25 +1277,25 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>CTL-HUM-04</v>
+        <v>CTL-DAT-06</v>
       </c>
       <c r="B28" t="str">
-        <v>Human oversight</v>
+        <v>Data</v>
       </c>
       <c r="C28" t="str">
-        <v>Autonomy limits for agents</v>
+        <v>Rules for data in generative AI tools</v>
       </c>
       <c r="D28" t="str">
-        <v>Document what an agent may do on its own, what it must never do, and the limits it works within (for example amounts, record types or number of actions), and enforce these limits technically.</v>
+        <v>Set clear rules on what information staff may enter into generative AI tools, and block personal, sensitive or classified data from external services unless explicitly approved.</v>
       </c>
       <c r="E28" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.9.4; NIST AI RMF: MAP 3.3, GOVERN 3.2; EU AI Act: Art. 14</v>
+        <v>Dubai AI Ethics: Privacy; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.2.3, A.9.2; NIST AI RMF: GOVERN 6.1, MEASURE 2.10</v>
       </c>
       <c r="F28" t="str">
         <v>Verified</v>
       </c>
       <c r="G28" t="str">
-        <v>Limited risk</v>
+        <v>Little or no risk</v>
       </c>
       <c r="H28" t="str">
         <v/>
@@ -1309,22 +1309,22 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>CTL-HUM-05</v>
+        <v>CTL-DAT-07</v>
       </c>
       <c r="B29" t="str">
-        <v>Human oversight</v>
+        <v>Data</v>
       </c>
       <c r="C29" t="str">
-        <v>Human approval for irreversible actions</v>
+        <v>Rights to training and grounding content</v>
       </c>
       <c r="D29" t="str">
-        <v>Require a named human to approve any agent action that cannot easily be undone or that significantly affects a person, such as payments, deletions, external messages or decisions on entitlements.</v>
+        <v>Confirm the organisation has the right to use the documents and content used to train, fine-tune or ground a model, and keep a record of that check.</v>
       </c>
       <c r="E29" t="str">
-        <v>UAE AI Charter: Human oversight; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.1.3; NIST AI RMF: MAP 3.5, GOVERN 3.2; EU AI Act: Art. 14</v>
+        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.7.3, A.7.5; NIST AI RMF: MAP 4.1, GOVERN 6.1; EU AI Act: Art. 53</v>
       </c>
       <c r="F29" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G29" t="str">
         <v>Limited risk</v>
@@ -1341,19 +1341,19 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>CTL-HUM-06</v>
+        <v>CTL-DAT-08</v>
       </c>
       <c r="B30" t="str">
-        <v>Human oversight</v>
+        <v>Data</v>
       </c>
       <c r="C30" t="str">
-        <v>Stop switch and rollback</v>
+        <v>Authoritative sources, no shadow copies</v>
       </c>
       <c r="D30" t="str">
-        <v>Provide a tested way for authorised staff to pause or shut down an agent immediately and to reverse or correct the actions it has already taken.</v>
+        <v>Have AI systems fetch government data from the authoritative (golden) source when it is needed and use it only for the authorised purpose. Do not keep copies for reuse or build parallel data stores.</v>
       </c>
       <c r="E30" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MANAGE 2.4; EU AI Act: Art. 14</v>
+        <v>UAE Gov Services Code: Code 5.3, Code 5.7, Data Sharing Policy Art. 5, Data Sharing Policy Art. 8</v>
       </c>
       <c r="F30" t="str">
         <v>Verified</v>
@@ -1373,22 +1373,22 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>CTL-SEC-01</v>
+        <v>CTL-DAT-09</v>
       </c>
       <c r="B31" t="str">
-        <v>Safety and security</v>
+        <v>Data</v>
       </c>
       <c r="C31" t="str">
-        <v>Test before deployment</v>
+        <v>Ask once</v>
       </c>
       <c r="D31" t="str">
-        <v>Test the system against defined accuracy and safety criteria, including unusual and edge-case inputs, in conditions close to real use before it goes live.</v>
+        <v>Design AI-led services so they never ask the customer for data or documents the government already holds and may use. Retrieve them from the source instead, and ask only for what is genuinely missing, saying why it is needed.</v>
       </c>
       <c r="E31" t="str">
-        <v>UAE AI Charter: Safety; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.5, MEASURE 2.6; EU AI Act: Art. 15</v>
+        <v>UAE Gov Services Code: Code 1.5, Code 5.4, Agentic Guide §03, Agentic Guide §06, Data Sharing Policy Art. 5, Data Sharing Policy Art. 8</v>
       </c>
       <c r="F31" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G31" t="str">
         <v>Limited risk</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>CTL-SEC-02</v>
+        <v>CTL-HUM-01</v>
       </c>
       <c r="B32" t="str">
-        <v>Safety and security</v>
+        <v>Human oversight</v>
       </c>
       <c r="C32" t="str">
-        <v>AI-specific security assessment</v>
+        <v>Defined human oversight model</v>
       </c>
       <c r="D32" t="str">
-        <v>Assess AI-specific threats such as prompt injection, data poisoning and data leakage through outputs, and include the resulting requirements in the system specification.</v>
+        <v>Decide and document, for each use case, where humans review, approve or monitor the system's outputs, and assign that role to people with the competence and authority to act.</v>
       </c>
       <c r="E32" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.2; NIST AI RMF: MEASURE 2.7; EU AI Act: Art. 15</v>
+        <v>UAE AI Charter: Human oversight; UAE Gov Services Code: Code 5.4, Agentic Guide §05, Agentic Reference p.7; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.1.3; NIST AI RMF: MAP 3.5, GOVERN 3.2; EU AI Act: Art. 14, Art. 26</v>
       </c>
       <c r="F32" t="str">
-        <v>Verified</v>
+        <v>Needs verification</v>
       </c>
       <c r="G32" t="str">
         <v>Limited risk</v>
@@ -1437,19 +1437,19 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>CTL-SEC-03</v>
+        <v>CTL-HUM-02</v>
       </c>
       <c r="B33" t="str">
-        <v>Safety and security</v>
+        <v>Human oversight</v>
       </c>
       <c r="C33" t="str">
-        <v>Safeguards on generated output</v>
+        <v>Right to challenge a decision</v>
       </c>
       <c r="D33" t="str">
-        <v>Put checks on generative output (grounding in approved sources, filters for harmful or false content, and human review where it matters) before it reaches customers or decisions.</v>
+        <v>Give people a clear route to challenge a significant AI-informed decision and have it reviewed by a human who can change it.</v>
       </c>
       <c r="E33" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.6</v>
+        <v>UAE Gov Services Code: Code 2.4, Agentic Guide §03, Agentic Guide §06; Dubai AI Ethics: Accountability; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.3; NIST AI RMF: MEASURE 3.3</v>
       </c>
       <c r="F33" t="str">
         <v>Verified</v>
@@ -1469,25 +1469,25 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>CTL-SEC-04</v>
+        <v>CTL-HUM-03</v>
       </c>
       <c r="B34" t="str">
-        <v>Safety and security</v>
+        <v>Human oversight</v>
       </c>
       <c r="C34" t="str">
-        <v>Least-privilege tools and permissions</v>
+        <v>Guard against over-reliance</v>
       </c>
       <c r="D34" t="str">
-        <v>Give an agent access only to the tools, systems and data it needs for its task, with read-only access by default and write access granted case by case.</v>
+        <v>Train reviewers to question AI outputs rather than rubber-stamp them, and check periodically how often they override the system.</v>
       </c>
       <c r="E34" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.4.4, A.6.2.2; NIST AI RMF: MAP 4.2; EU AI Act: Art. 15</v>
+        <v>ISO/IEC 42001: A.4.6; NIST AI RMF: MAP 3.4, GOVERN 3.2; EU AI Act: Art. 14</v>
       </c>
       <c r="F34" t="str">
         <v>Verified</v>
       </c>
       <c r="G34" t="str">
-        <v>Limited risk</v>
+        <v>High risk</v>
       </c>
       <c r="H34" t="str">
         <v/>
@@ -1501,19 +1501,19 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CTL-SEC-05</v>
+        <v>CTL-HUM-04</v>
       </c>
       <c r="B35" t="str">
-        <v>Safety and security</v>
+        <v>Human oversight</v>
       </c>
       <c r="C35" t="str">
-        <v>Sandbox and staged rollout for agents</v>
+        <v>Autonomy limits for agents</v>
       </c>
       <c r="D35" t="str">
-        <v>Run a new agent in a test or shadow mode, where its proposed actions are recorded but not executed, before giving it live access, and widen its scope in stages.</v>
+        <v>Document what an agent may do on its own, what it must never do, and the limits it works within (for example amounts, record types or number of actions), and enforce these limits technically.</v>
       </c>
       <c r="E35" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4, A.6.2.5; NIST AI RMF: MEASURE 2.3, MEASURE 2.6</v>
+        <v>UAE Gov Services Code: Code 5.4, Agentic Guide §05, Agentic Reference p.8; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.9.4; NIST AI RMF: MAP 3.3, GOVERN 3.2; EU AI Act: Art. 14</v>
       </c>
       <c r="F35" t="str">
         <v>Verified</v>
@@ -1533,22 +1533,22 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>CTL-SEC-06</v>
+        <v>CTL-HUM-05</v>
       </c>
       <c r="B36" t="str">
-        <v>Safety and security</v>
+        <v>Human oversight</v>
       </c>
       <c r="C36" t="str">
-        <v>Fallback and fail-safe</v>
+        <v>Human approval for irreversible actions</v>
       </c>
       <c r="D36" t="str">
-        <v>Define what happens when the system fails or is switched off, including a manual or non-AI fallback, so the service can continue safely.</v>
+        <v>Require a named human to approve any agent action that cannot easily be undone or that significantly affects a person, such as payments, deletions, external messages or decisions on entitlements.</v>
       </c>
       <c r="E36" t="str">
-        <v>SDAIA AI Ethics: Accountability &amp; Responsibility; NIST AI RMF: MANAGE 2.1, MEASURE 2.6; EU AI Act: Art. 15</v>
+        <v>UAE AI Charter: Human oversight; UAE Gov Services Code: Code 5.2, Agentic Guide §03; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.1.3; NIST AI RMF: MAP 3.5, GOVERN 3.2; EU AI Act: Art. 14</v>
       </c>
       <c r="F36" t="str">
-        <v>Verified</v>
+        <v>Needs verification</v>
       </c>
       <c r="G36" t="str">
         <v>Limited risk</v>
@@ -1565,25 +1565,25 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>CTL-SEC-07</v>
+        <v>CTL-HUM-06</v>
       </c>
       <c r="B37" t="str">
-        <v>Safety and security</v>
+        <v>Human oversight</v>
       </c>
       <c r="C37" t="str">
-        <v>Screen for prohibited uses</v>
+        <v>Stop switch and rollback</v>
       </c>
       <c r="D37" t="str">
-        <v>Screen every proposed use case against prohibited practices, such as social scoring or manipulating behaviour, and stop any that fall within them.</v>
+        <v>Provide a tested way for authorised staff to pause or shut down an agent immediately and to reverse or correct the actions it has already taken.</v>
       </c>
       <c r="E37" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.9.4; NIST AI RMF: MANAGE 1.1; EU AI Act: Art. 5</v>
+        <v>UAE Gov Services Code: Code 5.5; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MANAGE 2.4; EU AI Act: Art. 14</v>
       </c>
       <c r="F37" t="str">
         <v>Verified</v>
       </c>
       <c r="G37" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H37" t="str">
         <v/>
@@ -1597,19 +1597,19 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>CTL-MON-01</v>
+        <v>CTL-HUM-07</v>
       </c>
       <c r="B38" t="str">
-        <v>Monitoring</v>
+        <v>Human oversight</v>
       </c>
       <c r="C38" t="str">
-        <v>Performance monitoring with alerts</v>
+        <v>Specific approval for each agent action</v>
       </c>
       <c r="D38" t="str">
-        <v>Monitor the system in production against agreed measures, set alert thresholds in advance, and assign each alert to someone who must respond.</v>
+        <v>Before an agent acts for a customer, show a short plan and ask for approval of that specific action, the data it will use and any cost. Never rely on open-ended or blanket permission, and record each approval or refusal.</v>
       </c>
       <c r="E38" t="str">
-        <v>SDAIA AI Ethics: Accountability &amp; Responsibility, Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 4.1; EU AI Act: Art. 26, Art. 72</v>
+        <v>UAE Gov Services Code: Code 5.2, Agentic Guide §03, Agentic Guide §06</v>
       </c>
       <c r="F38" t="str">
         <v>Verified</v>
@@ -1629,19 +1629,19 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>CTL-MON-02</v>
+        <v>CTL-HUM-08</v>
       </c>
       <c r="B39" t="str">
-        <v>Monitoring</v>
+        <v>Human oversight</v>
       </c>
       <c r="C39" t="str">
-        <v>Event logging</v>
+        <v>One-step revocation of agent permissions</v>
       </c>
       <c r="D39" t="str">
-        <v>Log inputs, outputs, model version and key events automatically, and keep the logs long enough to investigate complaints and incidents.</v>
+        <v>Let customers stop an agent, or withdraw the permissions and consents they gave it, in a single step. Apply the withdrawal immediately and confirm it to them.</v>
       </c>
       <c r="E39" t="str">
-        <v>Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12, Art. 26</v>
+        <v>UAE Gov Services Code: Code 5.2, Agentic Guide §02, Agentic Guide §06</v>
       </c>
       <c r="F39" t="str">
         <v>Verified</v>
@@ -1661,25 +1661,25 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>CTL-MON-03</v>
+        <v>CTL-HUM-09</v>
       </c>
       <c r="B40" t="str">
-        <v>Monitoring</v>
+        <v>Human oversight</v>
       </c>
       <c r="C40" t="str">
-        <v>Agent action audit trail</v>
+        <v>Handover to a person with full context</v>
       </c>
       <c r="D40" t="str">
-        <v>Record every tool call and action an agent takes, with its inputs, the reason given, the result and any human approval, in a log the agent itself cannot alter.</v>
+        <v>Hand the case to a person when the customer asks, or when it is complex, sensitive, beyond what the AI is permitted to do, or failing. Pass on the request, context, actions taken and approvals so the customer never has to repeat their story.</v>
       </c>
       <c r="E40" t="str">
-        <v>Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12</v>
+        <v>UAE Gov Services Code: Code 1.7, Code 8.2, Agentic Guide §03, Agentic Guide §06</v>
       </c>
       <c r="F40" t="str">
         <v>Verified</v>
       </c>
       <c r="G40" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H40" t="str">
         <v/>
@@ -1693,25 +1693,25 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>CTL-MON-04</v>
+        <v>CTL-HUM-10</v>
       </c>
       <c r="B41" t="str">
-        <v>Monitoring</v>
+        <v>Human oversight</v>
       </c>
       <c r="C41" t="str">
-        <v>AI incident response</v>
+        <v>Explicit consent before any payment</v>
       </c>
       <c r="D41" t="str">
-        <v>Define how AI incidents and serious errors are reported, investigated, fixed and communicated to affected people and, where required, to regulators.</v>
+        <v>Before an agent makes a payment, show the fees, items, total, receiving entity and payment method, take the customer's explicit consent, and pay only through approved government payment channels. Follow up on any charge where the service was not completed.</v>
       </c>
       <c r="E41" t="str">
-        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.4; NIST AI RMF: MANAGE 4.3, MANAGE 2.3; EU AI Act: Art. 73</v>
+        <v>UAE Gov Services Code: Code 1.6, Code 5.8, Agentic Guide §03, Agentic Guide §06</v>
       </c>
       <c r="F41" t="str">
         <v>Verified</v>
       </c>
       <c r="G41" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H41" t="str">
         <v/>
@@ -1725,22 +1725,22 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>CTL-MON-05</v>
+        <v>CTL-SEC-01</v>
       </c>
       <c r="B42" t="str">
-        <v>Monitoring</v>
+        <v>Safety and security</v>
       </c>
       <c r="C42" t="str">
-        <v>Periodic review and re-tiering</v>
+        <v>Test before deployment</v>
       </c>
       <c r="D42" t="str">
-        <v>Review each system on a set schedule and after significant changes, check for drift and new risks, and update its risk tier and controls.</v>
+        <v>Test the system against defined accuracy and safety criteria, including unusual and edge-case inputs, in conditions close to real use before it goes live.</v>
       </c>
       <c r="E42" t="str">
-        <v>SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.5, MEASURE 3.1; EU AI Act: Art. 9</v>
+        <v>UAE AI Charter: Safety; UAE Gov Services Code: Code 8.8, Agentic Guide §06; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.5, MEASURE 2.6; EU AI Act: Art. 15</v>
       </c>
       <c r="F42" t="str">
-        <v>Verified</v>
+        <v>Needs verification</v>
       </c>
       <c r="G42" t="str">
         <v>Limited risk</v>
@@ -1757,25 +1757,25 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>CTL-MON-06</v>
+        <v>CTL-SEC-02</v>
       </c>
       <c r="B43" t="str">
-        <v>Monitoring</v>
+        <v>Safety and security</v>
       </c>
       <c r="C43" t="str">
-        <v>Channel to report concerns</v>
+        <v>AI-specific security assessment</v>
       </c>
       <c r="D43" t="str">
-        <v>Provide staff and users with a channel to report problems or concerns about an AI system, and track each report to closure.</v>
+        <v>Assess AI-specific threats such as prompt injection, data poisoning and data leakage through outputs, and include the resulting requirements in the system specification.</v>
       </c>
       <c r="E43" t="str">
-        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.3.3, A.8.3; NIST AI RMF: GOVERN 5.1, MEASURE 3.3</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.2; NIST AI RMF: MEASURE 2.7; EU AI Act: Art. 15</v>
       </c>
       <c r="F43" t="str">
         <v>Verified</v>
       </c>
       <c r="G43" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H43" t="str">
         <v/>
@@ -1789,25 +1789,25 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>CTL-MON-07</v>
+        <v>CTL-SEC-03</v>
       </c>
       <c r="B44" t="str">
-        <v>Monitoring</v>
+        <v>Safety and security</v>
       </c>
       <c r="C44" t="str">
-        <v>Safe decommissioning</v>
+        <v>Safeguards on generated output</v>
       </c>
       <c r="D44" t="str">
-        <v>Plan how a system will be retired, including data deletion or archiving, access removal and informing users, and follow the plan when it is withdrawn.</v>
+        <v>Put checks on generative output (grounding in approved sources, filters for harmful or false content, and human review where it matters) before it reaches customers or decisions.</v>
       </c>
       <c r="E44" t="str">
-        <v>Dubai AI Ethics: Security; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.7, MANAGE 2.4</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.6</v>
       </c>
       <c r="F44" t="str">
         <v>Verified</v>
       </c>
       <c r="G44" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H44" t="str">
         <v/>
@@ -1821,39 +1821,455 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
+        <v>CTL-SEC-04</v>
+      </c>
+      <c r="B45" t="str">
+        <v>Safety and security</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Least-privilege tools and permissions</v>
+      </c>
+      <c r="D45" t="str">
+        <v>Give an agent access only to the tools, systems and data it needs for its task, with read-only access by default and write access granted case by case.</v>
+      </c>
+      <c r="E45" t="str">
+        <v>UAE Gov Services Code: Code 5.1, Code 5.7; Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.4.4, A.6.2.2; NIST AI RMF: MAP 4.2; EU AI Act: Art. 15</v>
+      </c>
+      <c r="F45" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G45" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H45" t="str">
+        <v/>
+      </c>
+      <c r="I45" t="str">
+        <v/>
+      </c>
+      <c r="J45" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>CTL-SEC-05</v>
+      </c>
+      <c r="B46" t="str">
+        <v>Safety and security</v>
+      </c>
+      <c r="C46" t="str">
+        <v>Sandbox and staged rollout for agents</v>
+      </c>
+      <c r="D46" t="str">
+        <v>Run a new agent in a test or shadow mode, where its proposed actions are recorded but not executed, before giving it live access, and widen its scope in stages.</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4, A.6.2.5; NIST AI RMF: MEASURE 2.3, MEASURE 2.6</v>
+      </c>
+      <c r="F46" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G46" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H46" t="str">
+        <v/>
+      </c>
+      <c r="I46" t="str">
+        <v/>
+      </c>
+      <c r="J46" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>CTL-SEC-06</v>
+      </c>
+      <c r="B47" t="str">
+        <v>Safety and security</v>
+      </c>
+      <c r="C47" t="str">
+        <v>Fallback and fail-safe</v>
+      </c>
+      <c r="D47" t="str">
+        <v>Define what happens when the system fails or is switched off, including a manual or non-AI fallback, so the service can continue safely.</v>
+      </c>
+      <c r="E47" t="str">
+        <v>UAE Gov Services Code: Code 8.2; SDAIA AI Ethics: Accountability &amp; Responsibility; NIST AI RMF: MANAGE 2.1, MEASURE 2.6; EU AI Act: Art. 15</v>
+      </c>
+      <c r="F47" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G47" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H47" t="str">
+        <v/>
+      </c>
+      <c r="I47" t="str">
+        <v/>
+      </c>
+      <c r="J47" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>CTL-SEC-07</v>
+      </c>
+      <c r="B48" t="str">
+        <v>Safety and security</v>
+      </c>
+      <c r="C48" t="str">
+        <v>Screen for prohibited uses</v>
+      </c>
+      <c r="D48" t="str">
+        <v>Screen every proposed use case against prohibited practices, such as social scoring or manipulating behaviour, and stop any that fall within them.</v>
+      </c>
+      <c r="E48" t="str">
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.9.4; NIST AI RMF: MANAGE 1.1; EU AI Act: Art. 5</v>
+      </c>
+      <c r="F48" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G48" t="str">
+        <v>Little or no risk</v>
+      </c>
+      <c r="H48" t="str">
+        <v/>
+      </c>
+      <c r="I48" t="str">
+        <v/>
+      </c>
+      <c r="J48" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>CTL-SEC-08</v>
+      </c>
+      <c r="B49" t="str">
+        <v>Safety and security</v>
+      </c>
+      <c r="C49" t="str">
+        <v>Identity and authority check before each automated action</v>
+      </c>
+      <c r="D49" t="str">
+        <v>Before an agent or other automated process carries out an action, verify the identity of the person it acts for and confirm the action is within approved permissions. Block the action otherwise.</v>
+      </c>
+      <c r="E49" t="str">
+        <v>UAE Gov Services Code: Code 5.1; Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security</v>
+      </c>
+      <c r="F49" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G49" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H49" t="str">
+        <v/>
+      </c>
+      <c r="I49" t="str">
+        <v/>
+      </c>
+      <c r="J49" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>CTL-MON-01</v>
+      </c>
+      <c r="B50" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C50" t="str">
+        <v>Performance monitoring with alerts</v>
+      </c>
+      <c r="D50" t="str">
+        <v>Monitor the system in production against agreed measures, set alert thresholds in advance, and assign each alert to someone who must respond.</v>
+      </c>
+      <c r="E50" t="str">
+        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Accountability &amp; Responsibility, Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 4.1; EU AI Act: Art. 26, Art. 72</v>
+      </c>
+      <c r="F50" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G50" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H50" t="str">
+        <v/>
+      </c>
+      <c r="I50" t="str">
+        <v/>
+      </c>
+      <c r="J50" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>CTL-MON-02</v>
+      </c>
+      <c r="B51" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C51" t="str">
+        <v>Event logging</v>
+      </c>
+      <c r="D51" t="str">
+        <v>Log inputs, outputs, model version and key events automatically, and keep the logs long enough to investigate complaints and incidents.</v>
+      </c>
+      <c r="E51" t="str">
+        <v>UAE Gov Services Code: Code 5.6; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12, Art. 26</v>
+      </c>
+      <c r="F51" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G51" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H51" t="str">
+        <v/>
+      </c>
+      <c r="I51" t="str">
+        <v/>
+      </c>
+      <c r="J51" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>CTL-MON-03</v>
+      </c>
+      <c r="B52" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C52" t="str">
+        <v>Agent action audit trail</v>
+      </c>
+      <c r="D52" t="str">
+        <v>Record every tool call and action an agent takes, with its inputs, the reason given, the result and any human approval, in a log the agent itself cannot alter.</v>
+      </c>
+      <c r="E52" t="str">
+        <v>UAE Gov Services Code: Code 5.6, Agentic Guide §06, Agentic Reference p.9; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12</v>
+      </c>
+      <c r="F52" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G52" t="str">
+        <v>Little or no risk</v>
+      </c>
+      <c r="H52" t="str">
+        <v/>
+      </c>
+      <c r="I52" t="str">
+        <v/>
+      </c>
+      <c r="J52" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>CTL-MON-04</v>
+      </c>
+      <c r="B53" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C53" t="str">
+        <v>AI incident response</v>
+      </c>
+      <c r="D53" t="str">
+        <v>Define how AI incidents and serious errors are reported, investigated, fixed and communicated to affected people and, where required, to regulators.</v>
+      </c>
+      <c r="E53" t="str">
+        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.4; NIST AI RMF: MANAGE 4.3, MANAGE 2.3; EU AI Act: Art. 73</v>
+      </c>
+      <c r="F53" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G53" t="str">
+        <v>Little or no risk</v>
+      </c>
+      <c r="H53" t="str">
+        <v/>
+      </c>
+      <c r="I53" t="str">
+        <v/>
+      </c>
+      <c r="J53" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="str">
+        <v>CTL-MON-05</v>
+      </c>
+      <c r="B54" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C54" t="str">
+        <v>Periodic review and re-tiering</v>
+      </c>
+      <c r="D54" t="str">
+        <v>Review each system on a set schedule and after significant changes, check for drift and new risks, and update its risk tier and controls.</v>
+      </c>
+      <c r="E54" t="str">
+        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.5, MEASURE 3.1; EU AI Act: Art. 9</v>
+      </c>
+      <c r="F54" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G54" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H54" t="str">
+        <v/>
+      </c>
+      <c r="I54" t="str">
+        <v/>
+      </c>
+      <c r="J54" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="str">
+        <v>CTL-MON-06</v>
+      </c>
+      <c r="B55" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C55" t="str">
+        <v>Channel to report concerns</v>
+      </c>
+      <c r="D55" t="str">
+        <v>Provide staff and users with a channel to report problems or concerns about an AI system, and track each report to closure.</v>
+      </c>
+      <c r="E55" t="str">
+        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.3.3, A.8.3; NIST AI RMF: GOVERN 5.1, MEASURE 3.3</v>
+      </c>
+      <c r="F55" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G55" t="str">
+        <v>Little or no risk</v>
+      </c>
+      <c r="H55" t="str">
+        <v/>
+      </c>
+      <c r="I55" t="str">
+        <v/>
+      </c>
+      <c r="J55" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="str">
+        <v>CTL-MON-07</v>
+      </c>
+      <c r="B56" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C56" t="str">
+        <v>Safe decommissioning</v>
+      </c>
+      <c r="D56" t="str">
+        <v>Plan how a system will be retired, including data deletion or archiving, access removal and informing users, and follow the plan when it is withdrawn.</v>
+      </c>
+      <c r="E56" t="str">
+        <v>Dubai AI Ethics: Security; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.7, MANAGE 2.4</v>
+      </c>
+      <c r="F56" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G56" t="str">
+        <v>Little or no risk</v>
+      </c>
+      <c r="H56" t="str">
+        <v/>
+      </c>
+      <c r="I56" t="str">
+        <v/>
+      </c>
+      <c r="J56" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="str">
         <v>CTL-MON-08</v>
       </c>
-      <c r="B45" t="str">
+      <c r="B57" t="str">
         <v>Monitoring</v>
       </c>
-      <c r="C45" t="str">
+      <c r="C57" t="str">
         <v>Agent behaviour limits and auto-pause</v>
       </c>
-      <c r="D45" t="str">
+      <c r="D57" t="str">
         <v>Watch agents for unusual behaviour such as loops, spikes in actions or cost, or attempts to use tools outside their scope, and pause them automatically when limits are hit.</v>
       </c>
-      <c r="E45" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 2.4</v>
-      </c>
-      <c r="F45" t="str">
-        <v>Verified</v>
-      </c>
-      <c r="G45" t="str">
-        <v>Limited risk</v>
-      </c>
-      <c r="H45" t="str">
-        <v/>
-      </c>
-      <c r="I45" t="str">
-        <v/>
-      </c>
-      <c r="J45" t="str">
+      <c r="E57" t="str">
+        <v>UAE Gov Services Code: Code 5.5, Agentic Reference p.8; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 2.4</v>
+      </c>
+      <c r="F57" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G57" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H57" t="str">
+        <v/>
+      </c>
+      <c r="I57" t="str">
+        <v/>
+      </c>
+      <c r="J57" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="str">
+        <v>CTL-MON-09</v>
+      </c>
+      <c r="B58" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C58" t="str">
+        <v>KPIs and a continue/stop decision for each agent</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Set KPIs for each agent covering decision quality, bias and impact on the service against a pre-launch baseline. Review them on a fixed schedule alongside customer feedback, and record a decision to continue, modify or stop.</v>
+      </c>
+      <c r="E58" t="str">
+        <v>UAE Gov Services Code: Code 2.1, Code 2.3, Agentic Guide §05, Agentic Guide §06; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 1.1</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J45"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J58"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/en/control-checklist.xlsx
+++ b/public/templates/en/control-checklist.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J60"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1769,7 +1769,7 @@
         <v>Assess AI-specific threats such as prompt injection, data poisoning and data leakage through outputs, and include the resulting requirements in the system specification.</v>
       </c>
       <c r="E43" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.2; NIST AI RMF: MEASURE 2.7; EU AI Act: Art. 15</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.2; NIST AI RMF: MAP 1.6, MEASURE 2.7; EU AI Act: Art. 15</v>
       </c>
       <c r="F43" t="str">
         <v>Verified</v>
@@ -1981,19 +1981,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>CTL-MON-01</v>
+        <v>CTL-SEC-09</v>
       </c>
       <c r="B50" t="str">
-        <v>Monitoring</v>
+        <v>Safety and security</v>
       </c>
       <c r="C50" t="str">
-        <v>Performance monitoring with alerts</v>
+        <v>Red-team and jailbreak testing</v>
       </c>
       <c r="D50" t="str">
-        <v>Monitor the system in production against agreed measures, set alert thresholds in advance, and assign each alert to someone who must respond.</v>
+        <v>Before launch and after major changes, have people who did not build the system try to make it misbehave: jailbreaks, direct and indirect prompt injection (including through documents, emails or web pages it reads), extraction of confidential data, and misuse of its tools. Record what is found, fix it and test again.</v>
       </c>
       <c r="E50" t="str">
-        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Accountability &amp; Responsibility, Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 4.1; EU AI Act: Art. 26, Art. 72</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 1.3, MEASURE 2.6, MEASURE 2.7; EU AI Act: Art. 15, Art. 55</v>
       </c>
       <c r="F50" t="str">
         <v>Verified</v>
@@ -2013,19 +2013,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>CTL-MON-02</v>
+        <v>CTL-SEC-10</v>
       </c>
       <c r="B51" t="str">
-        <v>Monitoring</v>
+        <v>Safety and security</v>
       </c>
       <c r="C51" t="str">
-        <v>Event logging</v>
+        <v>Model supply chain security</v>
       </c>
       <c r="D51" t="str">
-        <v>Log inputs, outputs, model version and key events automatically, and keep the logs long enough to investigate complaints and incidents.</v>
+        <v>Keep a list of the models, datasets and AI libraries the system depends on, with their source, version and licence. Take them only from trusted sources, check their integrity before use, pin versions, and track vulnerabilities and upstream changes, so that a tampered or silently updated component cannot reach production.</v>
       </c>
       <c r="E51" t="str">
-        <v>UAE Gov Services Code: Code 5.6; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12, Art. 26</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.4.4, A.10.3; NIST AI RMF: GOVERN 6.1, MAP 4.1, MANAGE 3.2; EU AI Act: Art. 15, Art. 25</v>
       </c>
       <c r="F51" t="str">
         <v>Verified</v>
@@ -2045,25 +2045,25 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>CTL-MON-03</v>
+        <v>CTL-MON-01</v>
       </c>
       <c r="B52" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C52" t="str">
-        <v>Agent action audit trail</v>
+        <v>Performance monitoring with alerts</v>
       </c>
       <c r="D52" t="str">
-        <v>Record every tool call and action an agent takes, with its inputs, the reason given, the result and any human approval, in a log the agent itself cannot alter.</v>
+        <v>Monitor the system in production against agreed measures, set alert thresholds in advance, and assign each alert to someone who must respond.</v>
       </c>
       <c r="E52" t="str">
-        <v>UAE Gov Services Code: Code 5.6, Agentic Guide §06, Agentic Reference p.9; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12</v>
+        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Accountability &amp; Responsibility, Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 4.1; EU AI Act: Art. 26, Art. 72</v>
       </c>
       <c r="F52" t="str">
         <v>Verified</v>
       </c>
       <c r="G52" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H52" t="str">
         <v/>
@@ -2077,25 +2077,25 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>CTL-MON-04</v>
+        <v>CTL-MON-02</v>
       </c>
       <c r="B53" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C53" t="str">
-        <v>AI incident response</v>
+        <v>Event logging</v>
       </c>
       <c r="D53" t="str">
-        <v>Define how AI incidents and serious errors are reported, investigated, fixed and communicated to affected people and, where required, to regulators.</v>
+        <v>Log inputs, outputs, model version and key events automatically, and keep the logs long enough to investigate complaints and incidents.</v>
       </c>
       <c r="E53" t="str">
-        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.4; NIST AI RMF: MANAGE 4.3, MANAGE 2.3; EU AI Act: Art. 73</v>
+        <v>UAE Gov Services Code: Code 5.6; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12, Art. 26</v>
       </c>
       <c r="F53" t="str">
         <v>Verified</v>
       </c>
       <c r="G53" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H53" t="str">
         <v/>
@@ -2109,25 +2109,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>CTL-MON-05</v>
+        <v>CTL-MON-03</v>
       </c>
       <c r="B54" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C54" t="str">
-        <v>Periodic review and re-tiering</v>
+        <v>Agent action audit trail</v>
       </c>
       <c r="D54" t="str">
-        <v>Review each system on a set schedule and after significant changes, check for drift and new risks, and update its risk tier and controls.</v>
+        <v>Record every tool call and action an agent takes, with its inputs, the reason given, the result and any human approval, in a log the agent itself cannot alter.</v>
       </c>
       <c r="E54" t="str">
-        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.5, MEASURE 3.1; EU AI Act: Art. 9</v>
+        <v>UAE Gov Services Code: Code 5.6, Agentic Guide §06, Agentic Reference p.9; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12</v>
       </c>
       <c r="F54" t="str">
         <v>Verified</v>
       </c>
       <c r="G54" t="str">
-        <v>Limited risk</v>
+        <v>Little or no risk</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -2141,19 +2141,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>CTL-MON-06</v>
+        <v>CTL-MON-04</v>
       </c>
       <c r="B55" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C55" t="str">
-        <v>Channel to report concerns</v>
+        <v>AI incident response</v>
       </c>
       <c r="D55" t="str">
-        <v>Provide staff and users with a channel to report problems or concerns about an AI system, and track each report to closure.</v>
+        <v>Define how AI incidents and serious errors are reported, investigated, fixed and communicated to affected people and, where required, to regulators.</v>
       </c>
       <c r="E55" t="str">
-        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.3.3, A.8.3; NIST AI RMF: GOVERN 5.1, MEASURE 3.3</v>
+        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.4; NIST AI RMF: MANAGE 4.3, MANAGE 2.3; EU AI Act: Art. 73</v>
       </c>
       <c r="F55" t="str">
         <v>Verified</v>
@@ -2173,25 +2173,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>CTL-MON-07</v>
+        <v>CTL-MON-05</v>
       </c>
       <c r="B56" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C56" t="str">
-        <v>Safe decommissioning</v>
+        <v>Periodic review and re-tiering</v>
       </c>
       <c r="D56" t="str">
-        <v>Plan how a system will be retired, including data deletion or archiving, access removal and informing users, and follow the plan when it is withdrawn.</v>
+        <v>Review each system on a set schedule and after significant changes, check for drift and new risks, and update its risk tier and controls.</v>
       </c>
       <c r="E56" t="str">
-        <v>Dubai AI Ethics: Security; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.7, MANAGE 2.4</v>
+        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.5, MEASURE 3.1; EU AI Act: Art. 9</v>
       </c>
       <c r="F56" t="str">
         <v>Verified</v>
       </c>
       <c r="G56" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -2205,25 +2205,25 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>CTL-MON-08</v>
+        <v>CTL-MON-06</v>
       </c>
       <c r="B57" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C57" t="str">
-        <v>Agent behaviour limits and auto-pause</v>
+        <v>Channel to report concerns</v>
       </c>
       <c r="D57" t="str">
-        <v>Watch agents for unusual behaviour such as loops, spikes in actions or cost, or attempts to use tools outside their scope, and pause them automatically when limits are hit.</v>
+        <v>Provide staff and users with a channel to report problems or concerns about an AI system, and track each report to closure.</v>
       </c>
       <c r="E57" t="str">
-        <v>UAE Gov Services Code: Code 5.5, Agentic Reference p.8; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 2.4</v>
+        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.3.3, A.8.3; NIST AI RMF: GOVERN 5.1, MEASURE 3.3</v>
       </c>
       <c r="F57" t="str">
         <v>Verified</v>
       </c>
       <c r="G57" t="str">
-        <v>Limited risk</v>
+        <v>Little or no risk</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -2237,39 +2237,103 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>CTL-MON-09</v>
+        <v>CTL-MON-07</v>
       </c>
       <c r="B58" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C58" t="str">
+        <v>Safe decommissioning</v>
+      </c>
+      <c r="D58" t="str">
+        <v>Plan how a system will be retired, including data deletion or archiving, access removal and informing users, and follow the plan when it is withdrawn.</v>
+      </c>
+      <c r="E58" t="str">
+        <v>Dubai AI Ethics: Security; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.7, MANAGE 2.4</v>
+      </c>
+      <c r="F58" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G58" t="str">
+        <v>Little or no risk</v>
+      </c>
+      <c r="H58" t="str">
+        <v/>
+      </c>
+      <c r="I58" t="str">
+        <v/>
+      </c>
+      <c r="J58" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="str">
+        <v>CTL-MON-08</v>
+      </c>
+      <c r="B59" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C59" t="str">
+        <v>Agent behaviour limits and auto-pause</v>
+      </c>
+      <c r="D59" t="str">
+        <v>Watch agents for unusual behaviour such as loops, spikes in actions or cost, or attempts to use tools outside their scope, and pause them automatically when limits are hit.</v>
+      </c>
+      <c r="E59" t="str">
+        <v>UAE Gov Services Code: Code 5.5, Agentic Reference p.8; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 2.4</v>
+      </c>
+      <c r="F59" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G59" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H59" t="str">
+        <v/>
+      </c>
+      <c r="I59" t="str">
+        <v/>
+      </c>
+      <c r="J59" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="str">
+        <v>CTL-MON-09</v>
+      </c>
+      <c r="B60" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C60" t="str">
         <v>KPIs and a continue/stop decision for each agent</v>
       </c>
-      <c r="D58" t="str">
+      <c r="D60" t="str">
         <v>Set KPIs for each agent covering decision quality, bias and impact on the service against a pre-launch baseline. Review them on a fixed schedule alongside customer feedback, and record a decision to continue, modify or stop.</v>
       </c>
-      <c r="E58" t="str">
+      <c r="E60" t="str">
         <v>UAE Gov Services Code: Code 2.1, Code 2.3, Agentic Guide §05, Agentic Guide §06; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 1.1</v>
       </c>
-      <c r="F58" t="str">
-        <v>Verified</v>
-      </c>
-      <c r="G58" t="str">
-        <v>Limited risk</v>
-      </c>
-      <c r="H58" t="str">
-        <v/>
-      </c>
-      <c r="I58" t="str">
-        <v/>
-      </c>
-      <c r="J58" t="str">
+      <c r="F60" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J58"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J60"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/en/control-checklist.xlsx
+++ b/public/templates/en/control-checklist.xlsx
@@ -524,7 +524,7 @@
         <v>UAE AI Charter: Governance and accountability; UAE Gov Services Code: Agentic Reference p.9; Dubai AI Ethics: Accountability; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.3.2; NIST AI RMF: GOVERN 2.1</v>
       </c>
       <c r="F4" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G4" t="str">
         <v>Little or no risk</v>
@@ -681,10 +681,10 @@
         <v>Train staff who build, operate or rely on AI systems in what the systems can and cannot do and in their own responsibilities, proportionate to their role.</v>
       </c>
       <c r="E9" t="str">
-        <v>UAE AI Charter: Promoting AI awareness for an inclusive society; UAE Gov Services Code: Code 6.2; ISO/IEC 42001: A.4.6; NIST AI RMF: GOVERN 2.2, MAP 3.4; EU AI Act: Art. 4</v>
+        <v>UAE AI Charter: Promoting AI awareness for an inclusive future; UAE Gov Services Code: Code 6.2; ISO/IEC 42001: A.4.6; NIST AI RMF: GOVERN 2.2, MAP 3.4; EU AI Act: Art. 4</v>
       </c>
       <c r="F9" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G9" t="str">
         <v>Little or no risk</v>
@@ -844,7 +844,7 @@
         <v>UAE AI Charter: Transparency; UAE Gov Services Code: Code 5.6, Agentic Guide §06; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; EU AI Act: Art. 50</v>
       </c>
       <c r="F14" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G14" t="str">
         <v>Little or no risk</v>
@@ -1196,7 +1196,7 @@
         <v>UAE AI Charter: Data privacy; UAE Gov Services Code: Code 5.2, Code 5.7, Data Sharing Policy Art. 5; Dubai AI Ethics: Privacy; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.2.3, A.7.3; NIST AI RMF: MEASURE 2.10</v>
       </c>
       <c r="F25" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G25" t="str">
         <v>Little or no risk</v>
@@ -1260,7 +1260,7 @@
         <v>UAE AI Charter: Algorithmic bias; Dubai AI Ethics: Fairness; SDAIA AI Ethics: Fairness; ISO/IEC 42001: A.5.4, A.6.2.4; NIST AI RMF: MEASURE 2.11; EU AI Act: Art. 10</v>
       </c>
       <c r="F27" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G27" t="str">
         <v>Limited risk</v>
@@ -1420,7 +1420,7 @@
         <v>UAE AI Charter: Human oversight; UAE Gov Services Code: Code 5.4, Agentic Guide §05, Agentic Reference p.7; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.1.3; NIST AI RMF: MAP 3.5, GOVERN 3.2; EU AI Act: Art. 14, Art. 26</v>
       </c>
       <c r="F32" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G32" t="str">
         <v>Limited risk</v>
@@ -1548,7 +1548,7 @@
         <v>UAE AI Charter: Human oversight; UAE Gov Services Code: Code 5.2, Agentic Guide §03; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.1.3; NIST AI RMF: MAP 3.5, GOVERN 3.2; EU AI Act: Art. 14</v>
       </c>
       <c r="F36" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G36" t="str">
         <v>Limited risk</v>
@@ -1740,7 +1740,7 @@
         <v>UAE AI Charter: Safety; UAE Gov Services Code: Code 8.8, Agentic Guide §06; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.5, MEASURE 2.6; EU AI Act: Art. 15</v>
       </c>
       <c r="F42" t="str">
-        <v>Needs verification</v>
+        <v>Verified</v>
       </c>
       <c r="G42" t="str">
         <v>Limited risk</v>

--- a/public/templates/en/control-checklist.xlsx
+++ b/public/templates/en/control-checklist.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="16.83203125" customWidth="1"/>
@@ -1725,19 +1725,19 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>CTL-SEC-01</v>
+        <v>CTL-HUM-11</v>
       </c>
       <c r="B42" t="str">
-        <v>Safety and security</v>
+        <v>Human oversight</v>
       </c>
       <c r="C42" t="str">
-        <v>Test before deployment</v>
+        <v>Oversight effectiveness</v>
       </c>
       <c r="D42" t="str">
-        <v>Test the system against defined accuracy and safety criteria, including unusual and edge-case inputs, in conditions close to real use before it goes live.</v>
+        <v>Show that human review actually catches errors, not just that it happens: test reviewers with known flawed cases in testing or pilots, re-review a sample of approved cases blind, require approval reasons that cite evidence, cap each reviewer's volume, and treat near-100% approval rates or very short review times as triggers to investigate.</v>
       </c>
       <c r="E42" t="str">
-        <v>UAE AI Charter: Safety; UAE Gov Services Code: Code 8.8, Agentic Guide §06; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.5, MEASURE 2.6; EU AI Act: Art. 15</v>
+        <v>UAE AI Charter: Human oversight; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; NIST AI RMF: MAP 3.5, GOVERN 3.2; EU AI Act: Art. 14</v>
       </c>
       <c r="F42" t="str">
         <v>Verified</v>
@@ -1757,19 +1757,19 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>CTL-SEC-02</v>
+        <v>CTL-SEC-01</v>
       </c>
       <c r="B43" t="str">
         <v>Safety and security</v>
       </c>
       <c r="C43" t="str">
-        <v>AI-specific security assessment</v>
+        <v>Test before deployment</v>
       </c>
       <c r="D43" t="str">
-        <v>Assess AI-specific threats such as prompt injection, data poisoning and data leakage through outputs, and include the resulting requirements in the system specification.</v>
+        <v>Test the system against defined accuracy and safety criteria, including unusual and edge-case inputs, in conditions close to real use before it goes live.</v>
       </c>
       <c r="E43" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.2; NIST AI RMF: MAP 1.6, MEASURE 2.7; EU AI Act: Art. 15</v>
+        <v>UAE AI Charter: Safety; UAE Gov Services Code: Code 8.8, Agentic Guide §06; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.5, MEASURE 2.6; EU AI Act: Art. 15</v>
       </c>
       <c r="F43" t="str">
         <v>Verified</v>
@@ -1789,19 +1789,19 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>CTL-SEC-03</v>
+        <v>CTL-SEC-02</v>
       </c>
       <c r="B44" t="str">
         <v>Safety and security</v>
       </c>
       <c r="C44" t="str">
-        <v>Safeguards on generated output</v>
+        <v>AI-specific security assessment</v>
       </c>
       <c r="D44" t="str">
-        <v>Put checks on generative output (grounding in approved sources, filters for harmful or false content, and human review where it matters) before it reaches customers or decisions.</v>
+        <v>Assess AI-specific threats such as prompt injection, data poisoning and data leakage through outputs, and include the resulting requirements in the system specification.</v>
       </c>
       <c r="E44" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.6</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.2; NIST AI RMF: MAP 1.6, MEASURE 2.7; EU AI Act: Art. 15</v>
       </c>
       <c r="F44" t="str">
         <v>Verified</v>
@@ -1821,19 +1821,19 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>CTL-SEC-04</v>
+        <v>CTL-SEC-03</v>
       </c>
       <c r="B45" t="str">
         <v>Safety and security</v>
       </c>
       <c r="C45" t="str">
-        <v>Least-privilege tools and permissions</v>
+        <v>Safeguards on generated output</v>
       </c>
       <c r="D45" t="str">
-        <v>Give an agent access only to the tools, systems and data it needs for its task, with read-only access by default and write access granted case by case.</v>
+        <v>Put checks on generative output (grounding in approved sources, filters for harmful or false content, and human review where it matters) before it reaches customers or decisions.</v>
       </c>
       <c r="E45" t="str">
-        <v>UAE Gov Services Code: Code 5.1, Code 5.7; Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.4.4, A.6.2.2; NIST AI RMF: MAP 4.2; EU AI Act: Art. 15</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.6</v>
       </c>
       <c r="F45" t="str">
         <v>Verified</v>
@@ -1853,19 +1853,19 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>CTL-SEC-05</v>
+        <v>CTL-SEC-04</v>
       </c>
       <c r="B46" t="str">
         <v>Safety and security</v>
       </c>
       <c r="C46" t="str">
-        <v>Sandbox and staged rollout for agents</v>
+        <v>Least-privilege tools and permissions</v>
       </c>
       <c r="D46" t="str">
-        <v>Run a new agent in a test or shadow mode, where its proposed actions are recorded but not executed, before giving it live access, and widen its scope in stages.</v>
+        <v>Give an agent access only to the tools, systems and data it needs for its task, with read-only access by default and write access granted case by case.</v>
       </c>
       <c r="E46" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4, A.6.2.5; NIST AI RMF: MEASURE 2.3, MEASURE 2.6</v>
+        <v>UAE Gov Services Code: Code 5.1, Code 5.7; Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.4.4, A.6.2.2; NIST AI RMF: MAP 4.2; EU AI Act: Art. 15</v>
       </c>
       <c r="F46" t="str">
         <v>Verified</v>
@@ -1885,19 +1885,19 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>CTL-SEC-06</v>
+        <v>CTL-SEC-05</v>
       </c>
       <c r="B47" t="str">
         <v>Safety and security</v>
       </c>
       <c r="C47" t="str">
-        <v>Fallback and fail-safe</v>
+        <v>Sandbox and staged rollout for agents</v>
       </c>
       <c r="D47" t="str">
-        <v>Define what happens when the system fails or is switched off, including a manual or non-AI fallback, so the service can continue safely.</v>
+        <v>Run a new agent in a test or shadow mode, where its proposed actions are recorded but not executed, before giving it live access, and widen its scope in stages.</v>
       </c>
       <c r="E47" t="str">
-        <v>UAE Gov Services Code: Code 8.2; SDAIA AI Ethics: Accountability &amp; Responsibility; NIST AI RMF: MANAGE 2.1, MEASURE 2.6; EU AI Act: Art. 15</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4, A.6.2.5; NIST AI RMF: MEASURE 2.3, MEASURE 2.6</v>
       </c>
       <c r="F47" t="str">
         <v>Verified</v>
@@ -1917,25 +1917,25 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>CTL-SEC-07</v>
+        <v>CTL-SEC-06</v>
       </c>
       <c r="B48" t="str">
         <v>Safety and security</v>
       </c>
       <c r="C48" t="str">
-        <v>Screen for prohibited uses</v>
+        <v>Fallback and fail-safe</v>
       </c>
       <c r="D48" t="str">
-        <v>Screen every proposed use case against prohibited practices, such as social scoring or manipulating behaviour, and stop any that fall within them.</v>
+        <v>Define what happens when the system fails or is switched off, including a manual or non-AI fallback, so the service can continue safely.</v>
       </c>
       <c r="E48" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.9.4; NIST AI RMF: MANAGE 1.1; EU AI Act: Art. 5</v>
+        <v>UAE Gov Services Code: Code 8.2; SDAIA AI Ethics: Accountability &amp; Responsibility; NIST AI RMF: MANAGE 2.1, MEASURE 2.6; EU AI Act: Art. 15</v>
       </c>
       <c r="F48" t="str">
         <v>Verified</v>
       </c>
       <c r="G48" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H48" t="str">
         <v/>
@@ -1949,25 +1949,25 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>CTL-SEC-08</v>
+        <v>CTL-SEC-07</v>
       </c>
       <c r="B49" t="str">
         <v>Safety and security</v>
       </c>
       <c r="C49" t="str">
-        <v>Identity and authority check before each automated action</v>
+        <v>Screen for prohibited uses</v>
       </c>
       <c r="D49" t="str">
-        <v>Before an agent or other automated process carries out an action, verify the identity of the person it acts for and confirm the action is within approved permissions. Block the action otherwise.</v>
+        <v>Screen every proposed use case against prohibited practices, such as social scoring or manipulating behaviour, and stop any that fall within them.</v>
       </c>
       <c r="E49" t="str">
-        <v>UAE Gov Services Code: Code 5.1; Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.9.4; NIST AI RMF: MANAGE 1.1; EU AI Act: Art. 5</v>
       </c>
       <c r="F49" t="str">
         <v>Verified</v>
       </c>
       <c r="G49" t="str">
-        <v>Limited risk</v>
+        <v>Little or no risk</v>
       </c>
       <c r="H49" t="str">
         <v/>
@@ -1981,19 +1981,19 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>CTL-SEC-09</v>
+        <v>CTL-SEC-08</v>
       </c>
       <c r="B50" t="str">
         <v>Safety and security</v>
       </c>
       <c r="C50" t="str">
-        <v>Red-team and jailbreak testing</v>
+        <v>Identity and authority check before each automated action</v>
       </c>
       <c r="D50" t="str">
-        <v>Before launch and after major changes, have people who did not build the system try to make it misbehave: jailbreaks, direct and indirect prompt injection (including through documents, emails or web pages it reads), extraction of confidential data, and misuse of its tools. Record what is found, fix it and test again.</v>
+        <v>Before an agent or other automated process carries out an action, verify the identity of the person it acts for and confirm the action is within approved permissions. Block the action otherwise.</v>
       </c>
       <c r="E50" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 1.3, MEASURE 2.6, MEASURE 2.7; EU AI Act: Art. 15, Art. 55</v>
+        <v>UAE Gov Services Code: Code 5.1; Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security</v>
       </c>
       <c r="F50" t="str">
         <v>Verified</v>
@@ -2013,19 +2013,19 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>CTL-SEC-10</v>
+        <v>CTL-SEC-09</v>
       </c>
       <c r="B51" t="str">
         <v>Safety and security</v>
       </c>
       <c r="C51" t="str">
-        <v>Model supply chain security</v>
+        <v>Red-team and jailbreak testing</v>
       </c>
       <c r="D51" t="str">
-        <v>Keep a list of the models, datasets and AI libraries the system depends on, with their source, version and licence. Take them only from trusted sources, check their integrity before use, pin versions, and track vulnerabilities and upstream changes, so that a tampered or silently updated component cannot reach production.</v>
+        <v>Before launch and after major changes, have people who did not build the system try to make it misbehave: jailbreaks, direct and indirect prompt injection (including through documents, emails or web pages it reads), extraction of confidential data, and misuse of its tools. Record what is found, fix it and test again.</v>
       </c>
       <c r="E51" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.4.4, A.10.3; NIST AI RMF: GOVERN 6.1, MAP 4.1, MANAGE 3.2; EU AI Act: Art. 15, Art. 25</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 1.3, MEASURE 2.6, MEASURE 2.7; EU AI Act: Art. 15, Art. 55</v>
       </c>
       <c r="F51" t="str">
         <v>Verified</v>
@@ -2045,19 +2045,19 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>CTL-MON-01</v>
+        <v>CTL-SEC-10</v>
       </c>
       <c r="B52" t="str">
-        <v>Monitoring</v>
+        <v>Safety and security</v>
       </c>
       <c r="C52" t="str">
-        <v>Performance monitoring with alerts</v>
+        <v>Model supply chain security</v>
       </c>
       <c r="D52" t="str">
-        <v>Monitor the system in production against agreed measures, set alert thresholds in advance, and assign each alert to someone who must respond.</v>
+        <v>Keep a list of the models, datasets and AI libraries the system depends on, with their source, version and licence. Take them only from trusted sources, check their integrity before use, pin versions, and track vulnerabilities and upstream changes, so that a tampered or silently updated component cannot reach production.</v>
       </c>
       <c r="E52" t="str">
-        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Accountability &amp; Responsibility, Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 4.1; EU AI Act: Art. 26, Art. 72</v>
+        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.4.4, A.10.3; NIST AI RMF: GOVERN 6.1, MAP 4.1, MANAGE 3.2; EU AI Act: Art. 15, Art. 25</v>
       </c>
       <c r="F52" t="str">
         <v>Verified</v>
@@ -2077,19 +2077,19 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>CTL-MON-02</v>
+        <v>CTL-MON-01</v>
       </c>
       <c r="B53" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C53" t="str">
-        <v>Event logging</v>
+        <v>Performance monitoring with alerts</v>
       </c>
       <c r="D53" t="str">
-        <v>Log inputs, outputs, model version and key events automatically, and keep the logs long enough to investigate complaints and incidents.</v>
+        <v>Monitor the system in production against agreed measures, set alert thresholds in advance, and assign each alert to someone who must respond.</v>
       </c>
       <c r="E53" t="str">
-        <v>UAE Gov Services Code: Code 5.6; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12, Art. 26</v>
+        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Accountability &amp; Responsibility, Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 4.1; EU AI Act: Art. 26, Art. 72</v>
       </c>
       <c r="F53" t="str">
         <v>Verified</v>
@@ -2109,25 +2109,25 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>CTL-MON-03</v>
+        <v>CTL-MON-02</v>
       </c>
       <c r="B54" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C54" t="str">
-        <v>Agent action audit trail</v>
+        <v>Event logging</v>
       </c>
       <c r="D54" t="str">
-        <v>Record every tool call and action an agent takes, with its inputs, the reason given, the result and any human approval, in a log the agent itself cannot alter.</v>
+        <v>Log inputs, outputs, model version and key events automatically, and keep the logs long enough to investigate complaints and incidents.</v>
       </c>
       <c r="E54" t="str">
-        <v>UAE Gov Services Code: Code 5.6, Agentic Guide §06, Agentic Reference p.9; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12</v>
+        <v>UAE Gov Services Code: Code 5.6; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12, Art. 26</v>
       </c>
       <c r="F54" t="str">
         <v>Verified</v>
       </c>
       <c r="G54" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H54" t="str">
         <v/>
@@ -2141,19 +2141,19 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>CTL-MON-04</v>
+        <v>CTL-MON-03</v>
       </c>
       <c r="B55" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C55" t="str">
-        <v>AI incident response</v>
+        <v>Agent action audit trail</v>
       </c>
       <c r="D55" t="str">
-        <v>Define how AI incidents and serious errors are reported, investigated, fixed and communicated to affected people and, where required, to regulators.</v>
+        <v>Record every tool call and action an agent takes, with its inputs, the reason given, the result and any human approval, in a log the agent itself cannot alter.</v>
       </c>
       <c r="E55" t="str">
-        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.4; NIST AI RMF: MANAGE 4.3, MANAGE 2.3; EU AI Act: Art. 73</v>
+        <v>UAE Gov Services Code: Code 5.6, Agentic Guide §06, Agentic Reference p.9; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.6.2.8; NIST AI RMF: MEASURE 2.4; EU AI Act: Art. 12</v>
       </c>
       <c r="F55" t="str">
         <v>Verified</v>
@@ -2173,25 +2173,25 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>CTL-MON-05</v>
+        <v>CTL-MON-04</v>
       </c>
       <c r="B56" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C56" t="str">
-        <v>Periodic review and re-tiering</v>
+        <v>AI incident response</v>
       </c>
       <c r="D56" t="str">
-        <v>Review each system on a set schedule and after significant changes, check for drift and new risks, and update its risk tier and controls.</v>
+        <v>Define how AI incidents and serious errors are reported, investigated, fixed and communicated to affected people and, where required, to regulators.</v>
       </c>
       <c r="E56" t="str">
-        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.5, MEASURE 3.1; EU AI Act: Art. 9</v>
+        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.4; NIST AI RMF: MANAGE 4.3, MANAGE 2.3; EU AI Act: Art. 73</v>
       </c>
       <c r="F56" t="str">
         <v>Verified</v>
       </c>
       <c r="G56" t="str">
-        <v>Limited risk</v>
+        <v>Little or no risk</v>
       </c>
       <c r="H56" t="str">
         <v/>
@@ -2205,25 +2205,25 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>CTL-MON-06</v>
+        <v>CTL-MON-05</v>
       </c>
       <c r="B57" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C57" t="str">
-        <v>Channel to report concerns</v>
+        <v>Periodic review and re-tiering</v>
       </c>
       <c r="D57" t="str">
-        <v>Provide staff and users with a channel to report problems or concerns about an AI system, and track each report to closure.</v>
+        <v>Review each system on a set schedule and after significant changes, check for drift and new risks, and update its risk tier and controls.</v>
       </c>
       <c r="E57" t="str">
-        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.3.3, A.8.3; NIST AI RMF: GOVERN 5.1, MEASURE 3.3</v>
+        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.5, MEASURE 3.1; EU AI Act: Art. 9</v>
       </c>
       <c r="F57" t="str">
         <v>Verified</v>
       </c>
       <c r="G57" t="str">
-        <v>Little or no risk</v>
+        <v>Limited risk</v>
       </c>
       <c r="H57" t="str">
         <v/>
@@ -2237,19 +2237,19 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>CTL-MON-07</v>
+        <v>CTL-MON-06</v>
       </c>
       <c r="B58" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C58" t="str">
-        <v>Safe decommissioning</v>
+        <v>Channel to report concerns</v>
       </c>
       <c r="D58" t="str">
-        <v>Plan how a system will be retired, including data deletion or archiving, access removal and informing users, and follow the plan when it is withdrawn.</v>
+        <v>Provide staff and users with a channel to report problems or concerns about an AI system, and track each report to closure.</v>
       </c>
       <c r="E58" t="str">
-        <v>Dubai AI Ethics: Security; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.7, MANAGE 2.4</v>
+        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.3.3, A.8.3; NIST AI RMF: GOVERN 5.1, MEASURE 3.3</v>
       </c>
       <c r="F58" t="str">
         <v>Verified</v>
@@ -2269,25 +2269,25 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>CTL-MON-08</v>
+        <v>CTL-MON-07</v>
       </c>
       <c r="B59" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C59" t="str">
-        <v>Agent behaviour limits and auto-pause</v>
+        <v>Safe decommissioning</v>
       </c>
       <c r="D59" t="str">
-        <v>Watch agents for unusual behaviour such as loops, spikes in actions or cost, or attempts to use tools outside their scope, and pause them automatically when limits are hit.</v>
+        <v>Plan how a system will be retired, including data deletion or archiving, access removal and informing users, and follow the plan when it is withdrawn.</v>
       </c>
       <c r="E59" t="str">
-        <v>UAE Gov Services Code: Code 5.5, Agentic Reference p.8; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 2.4</v>
+        <v>Dubai AI Ethics: Security; ISO/IEC 42001: A.6.2.6; NIST AI RMF: GOVERN 1.7, MANAGE 2.4</v>
       </c>
       <c r="F59" t="str">
         <v>Verified</v>
       </c>
       <c r="G59" t="str">
-        <v>Limited risk</v>
+        <v>Little or no risk</v>
       </c>
       <c r="H59" t="str">
         <v/>
@@ -2301,39 +2301,71 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>CTL-MON-09</v>
+        <v>CTL-MON-08</v>
       </c>
       <c r="B60" t="str">
         <v>Monitoring</v>
       </c>
       <c r="C60" t="str">
+        <v>Agent behaviour limits and auto-pause</v>
+      </c>
+      <c r="D60" t="str">
+        <v>Watch agents for unusual behaviour such as loops, spikes in actions or cost, or attempts to use tools outside their scope, and pause them automatically when limits are hit.</v>
+      </c>
+      <c r="E60" t="str">
+        <v>UAE Gov Services Code: Code 5.5, Agentic Reference p.8; Dubai AI Ethics: Security; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 2.4</v>
+      </c>
+      <c r="F60" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G60" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H60" t="str">
+        <v/>
+      </c>
+      <c r="I60" t="str">
+        <v/>
+      </c>
+      <c r="J60" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="str">
+        <v>CTL-MON-09</v>
+      </c>
+      <c r="B61" t="str">
+        <v>Monitoring</v>
+      </c>
+      <c r="C61" t="str">
         <v>KPIs and a continue/stop decision for each agent</v>
       </c>
-      <c r="D60" t="str">
+      <c r="D61" t="str">
         <v>Set KPIs for each agent covering decision quality, bias and impact on the service against a pre-launch baseline. Review them on a fixed schedule alongside customer feedback, and record a decision to continue, modify or stop.</v>
       </c>
-      <c r="E60" t="str">
+      <c r="E61" t="str">
         <v>UAE Gov Services Code: Code 2.1, Code 2.3, Agentic Guide §05, Agentic Guide §06; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 1.1</v>
       </c>
-      <c r="F60" t="str">
-        <v>Verified</v>
-      </c>
-      <c r="G60" t="str">
-        <v>Limited risk</v>
-      </c>
-      <c r="H60" t="str">
-        <v/>
-      </c>
-      <c r="I60" t="str">
-        <v/>
-      </c>
-      <c r="J60" t="str">
+      <c r="F61" t="str">
+        <v>Verified</v>
+      </c>
+      <c r="G61" t="str">
+        <v>Limited risk</v>
+      </c>
+      <c r="H61" t="str">
+        <v/>
+      </c>
+      <c r="I61" t="str">
+        <v/>
+      </c>
+      <c r="J61" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J60"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J61"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/en/control-checklist.xlsx
+++ b/public/templates/en/control-checklist.xlsx
@@ -489,7 +489,7 @@
         <v>Adopt an AI policy approved by senior leadership that states the organisation's principles, risk appetite and approval rules for AI, and review it at least once a year.</v>
       </c>
       <c r="E3" t="str">
-        <v>Dubai AI Ethics: Accountability; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.2.2, A.2.4; NIST AI RMF: GOVERN 1.2, GOVERN 2.3</v>
+        <v>UAE AI Security Policy (CSC): 2.1.1; Dubai AI Ethics: Accountability; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.2.2, A.2.4; NIST AI RMF: GOVERN 1.2, GOVERN 2.3</v>
       </c>
       <c r="F3" t="str">
         <v>Verified</v>
@@ -553,7 +553,7 @@
         <v>Keep a single register of all AI systems in use or in development, with owner, purpose, data used, risk tier and status, and keep it current.</v>
       </c>
       <c r="E5" t="str">
-        <v>SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.4.2; NIST AI RMF: GOVERN 1.6</v>
+        <v>UAE AI Security Policy (CSC): 2.2.1; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.4.2; NIST AI RMF: GOVERN 1.6</v>
       </c>
       <c r="F5" t="str">
         <v>Verified</v>
@@ -585,7 +585,7 @@
         <v>Before approving a use case, assess its likely impact on individuals, groups and the organisation, record the result, and repeat the assessment when the system changes materially.</v>
       </c>
       <c r="E6" t="str">
-        <v>Dubai AI Ethics: Accountability; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.5.2, A.5.3, A.5.4; NIST AI RMF: MAP 1.1, MAP 5.1; EU AI Act: Art. 9, Art. 27</v>
+        <v>UAE PDPL: Art. 21; UAE AI Security Policy (CSC): 2.1.2; Dubai AI Ethics: Accountability; SDAIA AI Ethics: Accountability &amp; Responsibility; ISO/IEC 42001: A.5.2, A.5.3, A.5.4; NIST AI RMF: MAP 1.1, MAP 5.1; EU AI Act: Art. 9, Art. 27</v>
       </c>
       <c r="F6" t="str">
         <v>Verified</v>
@@ -649,7 +649,7 @@
         <v>Before buying or integrating a third-party model or AI service, check its documentation, data handling and known limitations, and set out responsibilities for oversight, incidents and updates in the contract.</v>
       </c>
       <c r="E8" t="str">
-        <v>Dubai AI Ethics: Accountability; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.10.2, A.10.3; NIST AI RMF: GOVERN 6.1, MANAGE 3.1; EU AI Act: Art. 25</v>
+        <v>UAE PDPL: Art. 8; UAE AI Security Policy (CSC): 2.1.3; Dubai AI Ethics: Accountability; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.10.2, A.10.3; NIST AI RMF: GOVERN 6.1, MANAGE 3.1; EU AI Act: Art. 25</v>
       </c>
       <c r="F8" t="str">
         <v>Verified</v>
@@ -681,7 +681,7 @@
         <v>Train staff who build, operate or rely on AI systems in what the systems can and cannot do and in their own responsibilities, proportionate to their role.</v>
       </c>
       <c r="E9" t="str">
-        <v>UAE AI Charter: Promoting AI awareness for an inclusive future; UAE Gov Services Code: Code 6.2; ISO/IEC 42001: A.4.6; NIST AI RMF: GOVERN 2.2, MAP 3.4; EU AI Act: Art. 4</v>
+        <v>UAE AI Charter: Promoting AI awareness for an inclusive future; UAE Gov Services Code: Code 6.2; UAE AI Security Policy (CSC): 2.5.1; ISO/IEC 42001: A.4.6; NIST AI RMF: GOVERN 2.2, MAP 3.4; EU AI Act: Art. 4</v>
       </c>
       <c r="F9" t="str">
         <v>Verified</v>
@@ -905,7 +905,7 @@
         <v>Provide a simple way for a person affected by a significant AI-informed decision to ask for, and receive, a plain-language explanation of the main factors behind it.</v>
       </c>
       <c r="E16" t="str">
-        <v>UAE Gov Services Code: Code 5.6; Dubai AI Ethics: Explainability; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; NIST AI RMF: MEASURE 2.9; EU AI Act: Art. 86</v>
+        <v>UAE Gov Services Code: Code 5.6; UAE PDPL: Art. 13; Dubai AI Ethics: Explainability; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.2; NIST AI RMF: MEASURE 2.9; EU AI Act: Art. 86</v>
       </c>
       <c r="F16" t="str">
         <v>Verified</v>
@@ -937,7 +937,7 @@
         <v>Inform people when a decision that significantly affects them is made or supported by an AI system, including employees affected by AI used at work.</v>
       </c>
       <c r="E17" t="str">
-        <v>UAE Gov Services Code: Code 5.6; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.5; EU AI Act: Art. 26</v>
+        <v>UAE Gov Services Code: Code 5.6; UAE PDPL: Art. 13; Dubai AI Ethics: Transparency; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.5; EU AI Act: Art. 26</v>
       </c>
       <c r="F17" t="str">
         <v>Verified</v>
@@ -1193,7 +1193,7 @@
         <v>Where personal data is involved, complete a privacy review and use only the minimum personal data the purpose needs, in line with the organisation's data protection policy.</v>
       </c>
       <c r="E25" t="str">
-        <v>UAE AI Charter: Data privacy; UAE Gov Services Code: Code 5.2, Code 5.7, Data Sharing Policy Art. 5; Dubai AI Ethics: Privacy; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.2.3, A.7.3; NIST AI RMF: MEASURE 2.10</v>
+        <v>UAE AI Charter: Data privacy; UAE Gov Services Code: Code 5.2, Code 5.7, Data Sharing Policy Art. 5; UAE PDPL: Art. 5, Art. 21; UAE AI Security Policy (CSC): 2.3.5; Dubai AI Ethics: Privacy; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.2.3, A.7.3; NIST AI RMF: MEASURE 2.10</v>
       </c>
       <c r="F25" t="str">
         <v>Verified</v>
@@ -1449,7 +1449,7 @@
         <v>Give people a clear route to challenge a significant AI-informed decision and have it reviewed by a human who can change it.</v>
       </c>
       <c r="E33" t="str">
-        <v>UAE Gov Services Code: Code 2.4, Agentic Guide §03, Agentic Guide §06; Dubai AI Ethics: Accountability; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.3; NIST AI RMF: MEASURE 3.3</v>
+        <v>UAE Gov Services Code: Code 2.4, Agentic Guide §03, Agentic Guide §06; UAE PDPL: Art. 18; Dubai AI Ethics: Accountability; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.3; NIST AI RMF: MEASURE 3.3</v>
       </c>
       <c r="F33" t="str">
         <v>Verified</v>
@@ -1769,7 +1769,7 @@
         <v>Test the system against defined accuracy and safety criteria, including unusual and edge-case inputs, in conditions close to real use before it goes live.</v>
       </c>
       <c r="E43" t="str">
-        <v>UAE AI Charter: Safety; UAE Gov Services Code: Code 8.8, Agentic Guide §06; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.5, MEASURE 2.6; EU AI Act: Art. 15</v>
+        <v>UAE AI Charter: Safety; UAE Gov Services Code: Code 8.8, Agentic Guide §06; UAE AI Security Policy (CSC): 2.4.4; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.5, MEASURE 2.6; EU AI Act: Art. 15</v>
       </c>
       <c r="F43" t="str">
         <v>Verified</v>
@@ -1801,7 +1801,7 @@
         <v>Assess AI-specific threats such as prompt injection, data poisoning and data leakage through outputs, and include the resulting requirements in the system specification.</v>
       </c>
       <c r="E44" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.2; NIST AI RMF: MAP 1.6, MEASURE 2.7; EU AI Act: Art. 15</v>
+        <v>UAE PDPL: Art. 20; UAE AI Security Policy (CSC): 2.1.2, 2.3.2; Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.2; NIST AI RMF: MAP 1.6, MEASURE 2.7; EU AI Act: Art. 15</v>
       </c>
       <c r="F44" t="str">
         <v>Verified</v>
@@ -1833,7 +1833,7 @@
         <v>Put checks on generative output (grounding in approved sources, filters for harmful or false content, and human review where it matters) before it reaches customers or decisions.</v>
       </c>
       <c r="E45" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.6</v>
+        <v>UAE AI Security Policy (CSC): 2.3.3; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 2.6</v>
       </c>
       <c r="F45" t="str">
         <v>Verified</v>
@@ -1897,7 +1897,7 @@
         <v>Run a new agent in a test or shadow mode, where its proposed actions are recorded but not executed, before giving it live access, and widen its scope in stages.</v>
       </c>
       <c r="E47" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4, A.6.2.5; NIST AI RMF: MEASURE 2.3, MEASURE 2.6</v>
+        <v>UAE AI Security Policy (CSC): 2.1.4; Dubai AI Ethics: Security; SDAIA AI Ethics: Reliability &amp; Safety; ISO/IEC 42001: A.6.2.4, A.6.2.5; NIST AI RMF: MEASURE 2.3, MEASURE 2.6</v>
       </c>
       <c r="F47" t="str">
         <v>Verified</v>
@@ -1929,7 +1929,7 @@
         <v>Define what happens when the system fails or is switched off, including a manual or non-AI fallback, so the service can continue safely.</v>
       </c>
       <c r="E48" t="str">
-        <v>UAE Gov Services Code: Code 8.2; SDAIA AI Ethics: Accountability &amp; Responsibility; NIST AI RMF: MANAGE 2.1, MEASURE 2.6; EU AI Act: Art. 15</v>
+        <v>UAE Gov Services Code: Code 8.2; UAE AI Security Policy (CSC): 2.4.2, 2.4.3; SDAIA AI Ethics: Accountability &amp; Responsibility; NIST AI RMF: MANAGE 2.1, MEASURE 2.6; EU AI Act: Art. 15</v>
       </c>
       <c r="F48" t="str">
         <v>Verified</v>
@@ -2025,7 +2025,7 @@
         <v>Before launch and after major changes, have people who did not build the system try to make it misbehave: jailbreaks, direct and indirect prompt injection (including through documents, emails or web pages it reads), extraction of confidential data, and misuse of its tools. Record what is found, fix it and test again.</v>
       </c>
       <c r="E51" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 1.3, MEASURE 2.6, MEASURE 2.7; EU AI Act: Art. 15, Art. 55</v>
+        <v>UAE AI Security Policy (CSC): 2.5.2; Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.6.2.4; NIST AI RMF: MEASURE 1.3, MEASURE 2.6, MEASURE 2.7; EU AI Act: Art. 15, Art. 55</v>
       </c>
       <c r="F51" t="str">
         <v>Verified</v>
@@ -2057,7 +2057,7 @@
         <v>Keep a list of the models, datasets and AI libraries the system depends on, with their source, version and licence. Take them only from trusted sources, check their integrity before use, pin versions, and track vulnerabilities and upstream changes, so that a tampered or silently updated component cannot reach production.</v>
       </c>
       <c r="E52" t="str">
-        <v>Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.4.4, A.10.3; NIST AI RMF: GOVERN 6.1, MAP 4.1, MANAGE 3.2; EU AI Act: Art. 15, Art. 25</v>
+        <v>UAE AI Security Policy (CSC): 2.1.3; Dubai AI Ethics: Security; SDAIA AI Ethics: Privacy &amp; Security; ISO/IEC 42001: A.4.4, A.10.3; NIST AI RMF: GOVERN 6.1, MAP 4.1, MANAGE 3.2; EU AI Act: Art. 15, Art. 25</v>
       </c>
       <c r="F52" t="str">
         <v>Verified</v>
@@ -2089,7 +2089,7 @@
         <v>Monitor the system in production against agreed measures, set alert thresholds in advance, and assign each alert to someone who must respond.</v>
       </c>
       <c r="E53" t="str">
-        <v>UAE Gov Services Code: Code 2.1; SDAIA AI Ethics: Accountability &amp; Responsibility, Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 4.1; EU AI Act: Art. 26, Art. 72</v>
+        <v>UAE Gov Services Code: Code 2.1; UAE AI Security Policy (CSC): 2.6.1; SDAIA AI Ethics: Accountability &amp; Responsibility, Reliability &amp; Safety; ISO/IEC 42001: A.6.2.6; NIST AI RMF: MEASURE 2.4, MANAGE 4.1; EU AI Act: Art. 26, Art. 72</v>
       </c>
       <c r="F53" t="str">
         <v>Verified</v>
@@ -2185,7 +2185,7 @@
         <v>Define how AI incidents and serious errors are reported, investigated, fixed and communicated to affected people and, where required, to regulators.</v>
       </c>
       <c r="E56" t="str">
-        <v>SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.4; NIST AI RMF: MANAGE 4.3, MANAGE 2.3; EU AI Act: Art. 73</v>
+        <v>UAE PDPL: Art. 9; UAE AI Security Policy (CSC): 2.6.2, 2.6.3; SDAIA AI Ethics: Transparency &amp; Explainability; ISO/IEC 42001: A.8.4; NIST AI RMF: MANAGE 4.3, MANAGE 2.3; EU AI Act: Art. 73</v>
       </c>
       <c r="F56" t="str">
         <v>Verified</v>
